--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G733"/>
+  <dimension ref="A1:G735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20209,6 +20209,60 @@
         <v>359.05</v>
       </c>
       <c r="G733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>348.2</v>
+      </c>
+      <c r="C734" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="D734" t="n">
+        <v>345.78</v>
+      </c>
+      <c r="E734" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="F734" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>348.96</v>
+      </c>
+      <c r="C735" t="n">
+        <v>349.11</v>
+      </c>
+      <c r="D735" t="n">
+        <v>347.17</v>
+      </c>
+      <c r="E735" t="n">
+        <v>348.89</v>
+      </c>
+      <c r="F735" t="n">
+        <v>356.63</v>
+      </c>
+      <c r="G735" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20225,7 +20279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B763"/>
+  <dimension ref="A1:B765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27858,6 +27912,26 @@
       </c>
       <c r="B763" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -28026,28 +28100,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01404375945153997</v>
+        <v>0.0125608031588397</v>
       </c>
       <c r="J2" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K2" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006832763748647608</v>
+        <v>0.0005492636563262376</v>
       </c>
       <c r="M2" t="n">
-        <v>2.941823224979728</v>
+        <v>2.939269078539795</v>
       </c>
       <c r="N2" t="n">
-        <v>15.1293267090082</v>
+        <v>15.10757669054104</v>
       </c>
       <c r="O2" t="n">
-        <v>3.889643519528261</v>
+        <v>3.886846625548922</v>
       </c>
       <c r="P2" t="n">
-        <v>350.8678262434486</v>
+        <v>350.8834981083443</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28104,28 +28178,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05925752807911081</v>
+        <v>0.0562111873597962</v>
       </c>
       <c r="J3" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K3" t="n">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01002470242904041</v>
+        <v>0.009043658245888708</v>
       </c>
       <c r="M3" t="n">
-        <v>3.409277614254008</v>
+        <v>3.412068813170496</v>
       </c>
       <c r="N3" t="n">
-        <v>18.19752908778318</v>
+        <v>18.22857556505227</v>
       </c>
       <c r="O3" t="n">
-        <v>4.26585619633189</v>
+        <v>4.269493595855634</v>
       </c>
       <c r="P3" t="n">
-        <v>352.9239362169965</v>
+        <v>352.9561724725983</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28182,28 +28256,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1321805070389032</v>
+        <v>0.1296381135294482</v>
       </c>
       <c r="J4" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K4" t="n">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03368394610523329</v>
+        <v>0.03256260359352747</v>
       </c>
       <c r="M4" t="n">
-        <v>4.205380731691241</v>
+        <v>4.206867729731254</v>
       </c>
       <c r="N4" t="n">
-        <v>26.30289493488569</v>
+        <v>26.28851110289492</v>
       </c>
       <c r="O4" t="n">
-        <v>5.128634802253489</v>
+        <v>5.127232304362161</v>
       </c>
       <c r="P4" t="n">
-        <v>347.5640796577996</v>
+        <v>347.5909797000165</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28260,28 +28334,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3075335251064584</v>
+        <v>0.3047148164399062</v>
       </c>
       <c r="J5" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K5" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1246806095832494</v>
+        <v>0.1231211514490373</v>
       </c>
       <c r="M5" t="n">
-        <v>4.793558871421316</v>
+        <v>4.798018060012874</v>
       </c>
       <c r="N5" t="n">
-        <v>34.81998329292663</v>
+        <v>34.79416487171513</v>
       </c>
       <c r="O5" t="n">
-        <v>5.900845981122251</v>
+        <v>5.898657887326161</v>
       </c>
       <c r="P5" t="n">
-        <v>345.8296738498907</v>
+        <v>345.8594534924657</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28338,28 +28412,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2447895098817064</v>
+        <v>0.2426242592333396</v>
       </c>
       <c r="J6" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K6" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08987378043197969</v>
+        <v>0.0888146692219568</v>
       </c>
       <c r="M6" t="n">
-        <v>4.623184013735731</v>
+        <v>4.623839716748851</v>
       </c>
       <c r="N6" t="n">
-        <v>31.82220101650744</v>
+        <v>31.77626209150415</v>
       </c>
       <c r="O6" t="n">
-        <v>5.641117000781622</v>
+        <v>5.637043736880543</v>
       </c>
       <c r="P6" t="n">
-        <v>354.1934615541464</v>
+        <v>354.2163381866048</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28397,7 +28471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G733"/>
+  <dimension ref="A1:G735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55485,6 +55559,80 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-37.3595875339552,175.93797071966242</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-37.36029689452525,175.93786287505395</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>-37.3610060768531,175.93772286774544</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-37.3617226419466,175.93768647004615</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-37.36243856550643,175.9377249703241</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-37.359588277397705,175.93797924398368</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-37.3602970598833,175.93786489541358</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-37.36100703113835,175.9377385057274</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-37.361722688861875,175.9376877098149</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-37.36243849769101,175.93772271524583</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G735"/>
+  <dimension ref="A1:G737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20263,6 +20263,60 @@
         <v>356.63</v>
       </c>
       <c r="G735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="C736" t="n">
+        <v>348.94</v>
+      </c>
+      <c r="D736" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="E736" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="F736" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>349.89</v>
+      </c>
+      <c r="C737" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="D737" t="n">
+        <v>348.58</v>
+      </c>
+      <c r="E737" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="F737" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="G737" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20279,7 +20333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B765"/>
+  <dimension ref="A1:B767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27932,6 +27986,26 @@
       </c>
       <c r="B765" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -28100,28 +28174,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0125608031588397</v>
+        <v>0.01150438832981134</v>
       </c>
       <c r="J2" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="K2" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005492636563262376</v>
+        <v>0.0004632606033764253</v>
       </c>
       <c r="M2" t="n">
-        <v>2.939269078539795</v>
+        <v>2.935163541509383</v>
       </c>
       <c r="N2" t="n">
-        <v>15.10757669054104</v>
+        <v>15.07709458075523</v>
       </c>
       <c r="O2" t="n">
-        <v>3.886846625548922</v>
+        <v>3.882923458008827</v>
       </c>
       <c r="P2" t="n">
-        <v>350.8834981083443</v>
+        <v>350.8946943289442</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28178,28 +28252,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0562111873597962</v>
+        <v>0.05361892653306063</v>
       </c>
       <c r="J3" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="K3" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009043658245888708</v>
+        <v>0.008257533720153032</v>
       </c>
       <c r="M3" t="n">
-        <v>3.412068813170496</v>
+        <v>3.41305075685535</v>
       </c>
       <c r="N3" t="n">
-        <v>18.22857556505227</v>
+        <v>18.23939393886957</v>
       </c>
       <c r="O3" t="n">
-        <v>4.269493595855634</v>
+        <v>4.270760346691157</v>
       </c>
       <c r="P3" t="n">
-        <v>352.9561724725983</v>
+        <v>352.9836796466191</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28256,28 +28330,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1296381135294482</v>
+        <v>0.1280823956055914</v>
       </c>
       <c r="J4" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="K4" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03256260359352747</v>
+        <v>0.0319711516915786</v>
       </c>
       <c r="M4" t="n">
-        <v>4.206867729731254</v>
+        <v>4.203283090748792</v>
       </c>
       <c r="N4" t="n">
-        <v>26.28851110289492</v>
+        <v>26.23822921854462</v>
       </c>
       <c r="O4" t="n">
-        <v>5.127232304362161</v>
+        <v>5.12232654352928</v>
       </c>
       <c r="P4" t="n">
-        <v>347.5909797000165</v>
+        <v>347.6074878815977</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28334,28 +28408,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3047148164399062</v>
+        <v>0.3027495412149219</v>
       </c>
       <c r="J5" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="K5" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1231211514490373</v>
+        <v>0.1222720812242057</v>
       </c>
       <c r="M5" t="n">
-        <v>4.798018060012874</v>
+        <v>4.797117338940539</v>
       </c>
       <c r="N5" t="n">
-        <v>34.79416487171513</v>
+        <v>34.73382734026001</v>
       </c>
       <c r="O5" t="n">
-        <v>5.898657887326161</v>
+        <v>5.893541154540283</v>
       </c>
       <c r="P5" t="n">
-        <v>345.8594534924657</v>
+        <v>345.880273712076</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28412,28 +28486,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2426242592333396</v>
+        <v>0.2410573010593993</v>
       </c>
       <c r="J6" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="K6" t="n">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0888146692219568</v>
+        <v>0.08820093452862643</v>
       </c>
       <c r="M6" t="n">
-        <v>4.623839716748851</v>
+        <v>4.620792167173261</v>
       </c>
       <c r="N6" t="n">
-        <v>31.77626209150415</v>
+        <v>31.71170415603599</v>
       </c>
       <c r="O6" t="n">
-        <v>5.637043736880543</v>
+        <v>5.631314602829075</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2163381866048</v>
+        <v>354.2329386092351</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28471,7 +28545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G735"/>
+  <dimension ref="A1:G737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55633,6 +55707,80 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>-37.35958806219073,175.937976776417</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>-37.36029690371181,175.93786298729617</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>-37.36100747738614,175.93774581845284</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-37.36172311109876,175.9376988677335</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-37.3624387587802,175.93773139729717</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>-37.359589187135725,175.9379896750612</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>-37.36029843786572,175.9378817317437</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>-37.36100799915221,175.93775436871653</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-37.36172349494957,175.93770901129596</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-37.36243901308726,175.93773985384067</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G737"/>
+  <dimension ref="A1:G738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20319,6 +20319,33 @@
       <c r="G737" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:06:07+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>349.64</v>
+      </c>
+      <c r="C738" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="D738" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="E738" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="F738" t="n">
+        <v>357.33</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20333,7 +20360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B767"/>
+  <dimension ref="A1:B768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28006,6 +28033,16 @@
       </c>
       <c r="B767" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -28174,28 +28211,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01150438832981134</v>
+        <v>0.01107047169044239</v>
       </c>
       <c r="J2" t="n">
+        <v>737</v>
+      </c>
+      <c r="K2" t="n">
         <v>736</v>
       </c>
-      <c r="K2" t="n">
-        <v>735</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0004632606033764253</v>
+        <v>0.0004301890842149936</v>
       </c>
       <c r="M2" t="n">
-        <v>2.935163541509383</v>
+        <v>2.932780299181999</v>
       </c>
       <c r="N2" t="n">
-        <v>15.07709458075523</v>
+        <v>15.0599066578106</v>
       </c>
       <c r="O2" t="n">
-        <v>3.882923458008827</v>
+        <v>3.880709555971769</v>
       </c>
       <c r="P2" t="n">
-        <v>350.8946943289442</v>
+        <v>350.8993015140397</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28252,28 +28289,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05361892653306063</v>
+        <v>0.05242451354823083</v>
       </c>
       <c r="J3" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K3" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008257533720153032</v>
+        <v>0.007909451852976424</v>
       </c>
       <c r="M3" t="n">
-        <v>3.41305075685535</v>
+        <v>3.413124893912735</v>
       </c>
       <c r="N3" t="n">
-        <v>18.23939393886957</v>
+        <v>18.2395447131507</v>
       </c>
       <c r="O3" t="n">
-        <v>4.270760346691157</v>
+        <v>4.270777998579497</v>
       </c>
       <c r="P3" t="n">
-        <v>352.9836796466191</v>
+        <v>352.9963770400282</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28330,28 +28367,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1280823956055914</v>
+        <v>0.1275808026243309</v>
       </c>
       <c r="J4" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K4" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0319711516915786</v>
+        <v>0.03181659830373185</v>
       </c>
       <c r="M4" t="n">
-        <v>4.203283090748792</v>
+        <v>4.200085582584056</v>
       </c>
       <c r="N4" t="n">
-        <v>26.23822921854462</v>
+        <v>26.20684847477595</v>
       </c>
       <c r="O4" t="n">
-        <v>5.12232654352928</v>
+        <v>5.119262493248022</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6074878815977</v>
+        <v>347.6128201439686</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28408,28 +28445,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3027495412149219</v>
+        <v>0.3017846832146913</v>
       </c>
       <c r="J5" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K5" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1222720812242057</v>
+        <v>0.1218609033409056</v>
       </c>
       <c r="M5" t="n">
-        <v>4.797117338940539</v>
+        <v>4.796550599089603</v>
       </c>
       <c r="N5" t="n">
-        <v>34.73382734026001</v>
+        <v>34.7029909850376</v>
       </c>
       <c r="O5" t="n">
-        <v>5.893541154540283</v>
+        <v>5.890924459287999</v>
       </c>
       <c r="P5" t="n">
-        <v>345.880273712076</v>
+        <v>345.8905139993026</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28486,28 +28523,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2410573010593993</v>
+        <v>0.2401534785550455</v>
       </c>
       <c r="J6" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K6" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08820093452862643</v>
+        <v>0.08780387229479325</v>
       </c>
       <c r="M6" t="n">
-        <v>4.620792167173261</v>
+        <v>4.619986152590379</v>
       </c>
       <c r="N6" t="n">
-        <v>31.71170415603599</v>
+        <v>31.68297231574879</v>
       </c>
       <c r="O6" t="n">
-        <v>5.631314602829075</v>
+        <v>5.628762947197971</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2329386092351</v>
+        <v>354.2425311109755</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28545,7 +28582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G737"/>
+  <dimension ref="A1:G738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55781,6 +55818,43 @@
         </is>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:06:07+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>-37.35958894258258,175.93798687100806</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>-37.36029796935196,175.9378760073914</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-37.36100841107234,175.93776111892475</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-37.36172332434933,175.937704503046</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-37.362438735044854,175.93773060801976</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G738"/>
+  <dimension ref="A1:G741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20346,6 +20346,87 @@
       <c r="G738" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 21:59:52+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>349.47</v>
+      </c>
+      <c r="C739" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="D739" t="n">
+        <v>349.95</v>
+      </c>
+      <c r="E739" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="F739" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>349.88</v>
+      </c>
+      <c r="C740" t="n">
+        <v>350.53</v>
+      </c>
+      <c r="D740" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="E740" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="F740" t="n">
+        <v>359.53</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>350.2</v>
+      </c>
+      <c r="C741" t="n">
+        <v>350.91</v>
+      </c>
+      <c r="D741" t="n">
+        <v>352.42</v>
+      </c>
+      <c r="E741" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="F741" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B768"/>
+  <dimension ref="A1:B771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28043,6 +28124,36 @@
       </c>
       <c r="B768" t="n">
         <v>0.49</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -28211,28 +28322,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01107047169044239</v>
+        <v>0.009956631913217925</v>
       </c>
       <c r="J2" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K2" t="n">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004301890842149936</v>
+        <v>0.0003510154264245724</v>
       </c>
       <c r="M2" t="n">
-        <v>2.932780299181999</v>
+        <v>2.924938397393428</v>
       </c>
       <c r="N2" t="n">
-        <v>15.0599066578106</v>
+        <v>15.00633873019831</v>
       </c>
       <c r="O2" t="n">
-        <v>3.880709555971769</v>
+        <v>3.873801586322964</v>
       </c>
       <c r="P2" t="n">
-        <v>350.8993015140397</v>
+        <v>350.9111767661025</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28289,28 +28400,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05242451354823083</v>
+        <v>0.04922847311724796</v>
       </c>
       <c r="J3" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K3" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007909451852976424</v>
+        <v>0.007021412799603777</v>
       </c>
       <c r="M3" t="n">
-        <v>3.413124893912735</v>
+        <v>3.411814196319477</v>
       </c>
       <c r="N3" t="n">
-        <v>18.2395447131507</v>
+        <v>18.2249928213391</v>
       </c>
       <c r="O3" t="n">
-        <v>4.270777998579497</v>
+        <v>4.269074000452452</v>
       </c>
       <c r="P3" t="n">
-        <v>352.9963770400282</v>
+        <v>353.0304997095166</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28367,28 +28478,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1275808026243309</v>
+        <v>0.1281850991796468</v>
       </c>
       <c r="J4" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K4" t="n">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03181659830373185</v>
+        <v>0.03238288919454868</v>
       </c>
       <c r="M4" t="n">
-        <v>4.200085582584056</v>
+        <v>4.188622795162194</v>
       </c>
       <c r="N4" t="n">
-        <v>26.20684847477595</v>
+        <v>26.10852222126839</v>
       </c>
       <c r="O4" t="n">
-        <v>5.119262493248022</v>
+        <v>5.109649911810827</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6128201439686</v>
+        <v>347.6063565652864</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28445,28 +28556,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3017846832146913</v>
+        <v>0.3005660290426297</v>
       </c>
       <c r="J5" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K5" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1218609033409056</v>
+        <v>0.1219140754130146</v>
       </c>
       <c r="M5" t="n">
-        <v>4.796550599089603</v>
+        <v>4.784546541745772</v>
       </c>
       <c r="N5" t="n">
-        <v>34.7029909850376</v>
+        <v>34.58064981278486</v>
       </c>
       <c r="O5" t="n">
-        <v>5.890924459287999</v>
+        <v>5.88053142265092</v>
       </c>
       <c r="P5" t="n">
-        <v>345.8905139993026</v>
+        <v>345.9034892547519</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28523,28 +28634,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2401534785550455</v>
+        <v>0.2388055667581024</v>
       </c>
       <c r="J6" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="K6" t="n">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08780387229479325</v>
+        <v>0.08758629430038012</v>
       </c>
       <c r="M6" t="n">
-        <v>4.619986152590379</v>
+        <v>4.609320296867121</v>
       </c>
       <c r="N6" t="n">
-        <v>31.68297231574879</v>
+        <v>31.57291913804545</v>
       </c>
       <c r="O6" t="n">
-        <v>5.628762947197971</v>
+        <v>5.618978478161796</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2425311109755</v>
+        <v>354.2568856484992</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28582,7 +28693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G738"/>
+  <dimension ref="A1:G741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55855,6 +55966,117 @@
         </is>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 21:59:52+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>-37.3595887762864,175.937984964252</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>-37.36029804284434,175.937876905329</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-37.36100893970261,175.93776978169205</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-37.361723260374184,175.93770281245224</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-37.362438636712604,175.9377273381563</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>-37.35958917735359,175.93798956289908</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>-37.36029836437339,175.93788083380605</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>-37.361010868854386,175.9378013951682</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-37.36172450148751,175.937735609971</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-37.36243948101063,175.93775541388078</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>-37.35958949038151,175.93799315208707</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>-37.3602987134619,175.93788509900975</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>-37.36101063543433,175.93779757005004</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-37.361724787240824,175.93774316128986</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-37.36243974548816,175.9377642086861</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G741"/>
+  <dimension ref="A1:G742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20425,6 +20425,33 @@
         <v>360.31</v>
       </c>
       <c r="G741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="C742" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="D742" t="n">
+        <v>353.38</v>
+      </c>
+      <c r="E742" t="n">
+        <v>353.76</v>
+      </c>
+      <c r="F742" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="G742" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20441,7 +20468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B771"/>
+  <dimension ref="A1:B773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28154,6 +28181,26 @@
       </c>
       <c r="B771" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -28322,28 +28369,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009956631913217925</v>
+        <v>0.01005868363640874</v>
       </c>
       <c r="J2" t="n">
+        <v>741</v>
+      </c>
+      <c r="K2" t="n">
         <v>740</v>
       </c>
-      <c r="K2" t="n">
-        <v>739</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0003510154264245724</v>
+        <v>0.0003593417271680055</v>
       </c>
       <c r="M2" t="n">
-        <v>2.924938397393428</v>
+        <v>2.921603699033613</v>
       </c>
       <c r="N2" t="n">
-        <v>15.00633873019831</v>
+        <v>14.98624029357062</v>
       </c>
       <c r="O2" t="n">
-        <v>3.873801586322964</v>
+        <v>3.871206568186542</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9111767661025</v>
+        <v>350.9100831231711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28400,28 +28447,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04922847311724796</v>
+        <v>0.04884583459993836</v>
       </c>
       <c r="J3" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K3" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007021412799603777</v>
+        <v>0.006933548774261999</v>
       </c>
       <c r="M3" t="n">
-        <v>3.411814196319477</v>
+        <v>3.408674579137013</v>
       </c>
       <c r="N3" t="n">
-        <v>18.2249928213391</v>
+        <v>18.20280517755516</v>
       </c>
       <c r="O3" t="n">
-        <v>4.269074000452452</v>
+        <v>4.266474560753312</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0304997095166</v>
+        <v>353.0346054561533</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28478,28 +28525,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1281850991796468</v>
+        <v>0.128847704312328</v>
       </c>
       <c r="J4" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K4" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03238288919454868</v>
+        <v>0.03279538470232568</v>
       </c>
       <c r="M4" t="n">
-        <v>4.188622795162194</v>
+        <v>4.186033016657465</v>
       </c>
       <c r="N4" t="n">
-        <v>26.10852222126839</v>
+        <v>26.08071642887346</v>
       </c>
       <c r="O4" t="n">
-        <v>5.109649911810827</v>
+        <v>5.106928277239994</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6063565652864</v>
+        <v>347.5992467510051</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28556,28 +28603,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3005660290426297</v>
+        <v>0.3005329493582439</v>
       </c>
       <c r="J5" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K5" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1219140754130146</v>
+        <v>0.1222194914829573</v>
       </c>
       <c r="M5" t="n">
-        <v>4.784546541745772</v>
+        <v>4.778289180800403</v>
       </c>
       <c r="N5" t="n">
-        <v>34.58064981278486</v>
+        <v>34.53400121222595</v>
       </c>
       <c r="O5" t="n">
-        <v>5.88053142265092</v>
+        <v>5.876563724850259</v>
       </c>
       <c r="P5" t="n">
-        <v>345.9034892547519</v>
+        <v>345.9038436029209</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28634,28 +28681,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2388055667581024</v>
+        <v>0.2387093533041374</v>
       </c>
       <c r="J6" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K6" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08758629430038012</v>
+        <v>0.08776703569083666</v>
       </c>
       <c r="M6" t="n">
-        <v>4.609320296867121</v>
+        <v>4.60366837800927</v>
       </c>
       <c r="N6" t="n">
-        <v>31.57291913804545</v>
+        <v>31.53047086045967</v>
       </c>
       <c r="O6" t="n">
-        <v>5.618978478161796</v>
+        <v>5.615199984013007</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2568856484992</v>
+        <v>354.2579162829164</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28693,7 +28740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G741"/>
+  <dimension ref="A1:G742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56077,6 +56124,43 @@
         </is>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>-37.359590801184716,175.93800818181208</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>-37.36030060588647,175.93790822090403</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-37.361011294502376,175.93780837038372</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-37.361724765915966,175.93774259775861</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>-37.36243972514376,175.9377635321626</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G742"/>
+  <dimension ref="A1:G747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20452,6 +20452,141 @@
         <v>360.25</v>
       </c>
       <c r="G742" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>352.12</v>
+      </c>
+      <c r="C743" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="D743" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="E743" t="n">
+        <v>354.15</v>
+      </c>
+      <c r="F743" t="n">
+        <v>360.02</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="C744" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="D744" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="E744" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="F744" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:03+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="C745" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="D745" t="n">
+        <v>348.97</v>
+      </c>
+      <c r="E745" t="n">
+        <v>350.46</v>
+      </c>
+      <c r="F745" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>349.94</v>
+      </c>
+      <c r="C746" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="D746" t="n">
+        <v>348.49</v>
+      </c>
+      <c r="E746" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="F746" t="n">
+        <v>355.98</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>349.5</v>
+      </c>
+      <c r="C747" t="n">
+        <v>349.16</v>
+      </c>
+      <c r="D747" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="E747" t="n">
+        <v>349.35</v>
+      </c>
+      <c r="F747" t="n">
+        <v>355.63</v>
+      </c>
+      <c r="G747" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20468,7 +20603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B773"/>
+  <dimension ref="A1:B778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28201,6 +28336,56 @@
       </c>
       <c r="B773" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -28369,28 +28554,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01005868363640874</v>
+        <v>0.009026352145174703</v>
       </c>
       <c r="J2" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="K2" t="n">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003593417271680055</v>
+        <v>0.0002936577808506646</v>
       </c>
       <c r="M2" t="n">
-        <v>2.921603699033613</v>
+        <v>2.908272343241534</v>
       </c>
       <c r="N2" t="n">
-        <v>14.98624029357062</v>
+        <v>14.89473748200733</v>
       </c>
       <c r="O2" t="n">
-        <v>3.871206568186542</v>
+        <v>3.859370088758958</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9100831231711</v>
+        <v>350.9211880880273</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28447,28 +28632,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04884583459993836</v>
+        <v>0.04334677414321632</v>
       </c>
       <c r="J3" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="K3" t="n">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006933548774261999</v>
+        <v>0.005515606649448057</v>
       </c>
       <c r="M3" t="n">
-        <v>3.408674579137013</v>
+        <v>3.406822341191201</v>
       </c>
       <c r="N3" t="n">
-        <v>18.20280517755516</v>
+        <v>18.19954102412071</v>
       </c>
       <c r="O3" t="n">
-        <v>4.266474560753312</v>
+        <v>4.266092008398402</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0346054561533</v>
+        <v>353.0937876716029</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28525,28 +28710,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.128847704312328</v>
+        <v>0.1271651689448667</v>
       </c>
       <c r="J4" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="K4" t="n">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03279538470232568</v>
+        <v>0.03240103290192331</v>
       </c>
       <c r="M4" t="n">
-        <v>4.186033016657465</v>
+        <v>4.173016333704912</v>
       </c>
       <c r="N4" t="n">
-        <v>26.08071642887346</v>
+        <v>25.94269383485808</v>
       </c>
       <c r="O4" t="n">
-        <v>5.106928277239994</v>
+        <v>5.093397081993321</v>
       </c>
       <c r="P4" t="n">
-        <v>347.5992467510051</v>
+        <v>347.6173773681059</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28603,28 +28788,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3005329493582439</v>
+        <v>0.2967371553953811</v>
       </c>
       <c r="J5" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="K5" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1222194914829573</v>
+        <v>0.1209176187306202</v>
       </c>
       <c r="M5" t="n">
-        <v>4.778289180800403</v>
+        <v>4.76994287264383</v>
       </c>
       <c r="N5" t="n">
-        <v>34.53400121222595</v>
+        <v>34.37252694519105</v>
       </c>
       <c r="O5" t="n">
-        <v>5.876563724850259</v>
+        <v>5.862808793163142</v>
       </c>
       <c r="P5" t="n">
-        <v>345.9038436029209</v>
+        <v>345.9446355350552</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28681,28 +28866,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2387093533041374</v>
+        <v>0.2339823046891165</v>
       </c>
       <c r="J6" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="K6" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08776703569083666</v>
+        <v>0.08557085064059811</v>
       </c>
       <c r="M6" t="n">
-        <v>4.60366837800927</v>
+        <v>4.600392413751127</v>
       </c>
       <c r="N6" t="n">
-        <v>31.53047086045967</v>
+        <v>31.41361046131611</v>
       </c>
       <c r="O6" t="n">
-        <v>5.615199984013007</v>
+        <v>5.604784604364035</v>
       </c>
       <c r="P6" t="n">
-        <v>354.2579162829164</v>
+        <v>354.3087084054447</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28740,7 +28925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G742"/>
+  <dimension ref="A1:G747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56161,6 +56346,191 @@
         </is>
       </c>
     </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>-37.3595913685467,175.9380146872156</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>-37.36030072531116,175.9379096800527</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>-37.36101139061638,175.93780994543238</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>-37.36172493224979,175.9377469933024</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>-37.36243964715684,175.93776093882258</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>-37.35958954907422,175.93799382505983</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>-37.360298107150165,175.9378776910244</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-37.361009166258235,175.93777349430664</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>-37.36172393424441,175.9377206200397</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>-37.36243880964167,175.93773308860585</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:03+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>-37.35958959798484,175.93799438587047</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-37.36029751002449,175.93787039528135</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-37.361008266900335,175.93775875635188</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-37.36172335846939,175.93770540469598</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>-37.36243850108176,175.93772282799975</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>-37.35958923604634,175.93799023587184</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>-37.36029746409173,175.93786983407037</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>-37.36100793736414,175.9377533561853</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-37.36172312389382,175.93769920585228</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>-37.36243827729052,175.93771538624148</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>-37.3595888056328,175.93798530073835</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>-37.36029710581609,175.93786545662456</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>-37.36100743619407,175.93774514343204</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-37.36172288505289,175.93769289430233</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>-37.36243815861316,175.93771143985452</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0201/nzd0201.xlsx
+++ b/data/nzd0201/nzd0201.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G747"/>
+  <dimension ref="A1:G752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20587,6 +20587,141 @@
         <v>355.63</v>
       </c>
       <c r="G747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:05+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="C748" t="n">
+        <v>350.21</v>
+      </c>
+      <c r="D748" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="E748" t="n">
+        <v>348.15</v>
+      </c>
+      <c r="F748" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="C749" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="D749" t="n">
+        <v>350.81</v>
+      </c>
+      <c r="E749" t="n">
+        <v>348.49</v>
+      </c>
+      <c r="F749" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:58:57+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="C750" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="D750" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="E750" t="n">
+        <v>348.49</v>
+      </c>
+      <c r="F750" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="C751" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="D751" t="n">
+        <v>349.22</v>
+      </c>
+      <c r="E751" t="n">
+        <v>347.46</v>
+      </c>
+      <c r="F751" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="C752" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="D752" t="n">
+        <v>347.56</v>
+      </c>
+      <c r="E752" t="n">
+        <v>346.36</v>
+      </c>
+      <c r="F752" t="n">
+        <v>353.61</v>
+      </c>
+      <c r="G752" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20603,7 +20738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B778"/>
+  <dimension ref="A1:B783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28386,6 +28521,56 @@
       </c>
       <c r="B778" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -28554,28 +28739,28 @@
         <v>0.0586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009026352145174703</v>
+        <v>0.01026826163811108</v>
       </c>
       <c r="J2" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K2" t="n">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002936577808506646</v>
+        <v>0.0003855155440054547</v>
       </c>
       <c r="M2" t="n">
-        <v>2.908272343241534</v>
+        <v>2.897951767754993</v>
       </c>
       <c r="N2" t="n">
-        <v>14.89473748200733</v>
+        <v>14.80510375929022</v>
       </c>
       <c r="O2" t="n">
-        <v>3.859370088758958</v>
+        <v>3.847740084684804</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9211880880273</v>
+        <v>350.9077983182512</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28632,28 +28817,28 @@
         <v>0.055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04334677414321632</v>
+        <v>0.03873181875440462</v>
       </c>
       <c r="J3" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K3" t="n">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005515606649448057</v>
+        <v>0.004455923545781393</v>
       </c>
       <c r="M3" t="n">
-        <v>3.406822341191201</v>
+        <v>3.40185338497491</v>
       </c>
       <c r="N3" t="n">
-        <v>18.19954102412071</v>
+        <v>18.15637262878476</v>
       </c>
       <c r="O3" t="n">
-        <v>4.266092008398402</v>
+        <v>4.261029526861409</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0937876716029</v>
+        <v>353.1436381809562</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28710,28 +28895,28 @@
         <v>0.1052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1271651689448667</v>
+        <v>0.1251649042037688</v>
       </c>
       <c r="J4" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K4" t="n">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03240103290192331</v>
+        <v>0.03185581408253302</v>
       </c>
       <c r="M4" t="n">
-        <v>4.173016333704912</v>
+        <v>4.154995907931923</v>
       </c>
       <c r="N4" t="n">
-        <v>25.94269383485808</v>
+        <v>25.79211875725865</v>
       </c>
       <c r="O4" t="n">
-        <v>5.093397081993321</v>
+        <v>5.078594171348864</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6173773681059</v>
+        <v>347.6389946121758</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28788,28 +28973,28 @@
         <v>0.1131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2967371553953811</v>
+        <v>0.2885091950573918</v>
       </c>
       <c r="J5" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K5" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1209176187306202</v>
+        <v>0.1158771267548429</v>
       </c>
       <c r="M5" t="n">
-        <v>4.76994287264383</v>
+        <v>4.78807746691098</v>
       </c>
       <c r="N5" t="n">
-        <v>34.37252694519105</v>
+        <v>34.38891135150721</v>
       </c>
       <c r="O5" t="n">
-        <v>5.862808793163142</v>
+        <v>5.864205943817732</v>
       </c>
       <c r="P5" t="n">
-        <v>345.9446355350552</v>
+        <v>346.0333653473993</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28866,28 +29051,28 @@
         <v>0.1158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2339823046891165</v>
+        <v>0.2268704040926209</v>
       </c>
       <c r="J6" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="K6" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08557085064059811</v>
+        <v>0.08154557798911899</v>
       </c>
       <c r="M6" t="n">
-        <v>4.600392413751127</v>
+        <v>4.610788532839531</v>
       </c>
       <c r="N6" t="n">
-        <v>31.41361046131611</v>
+        <v>31.3904169555855</v>
       </c>
       <c r="O6" t="n">
-        <v>5.604784604364035</v>
+        <v>5.602715141392207</v>
       </c>
       <c r="P6" t="n">
-        <v>354.3087084054447</v>
+        <v>354.3854041528136</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28925,7 +29110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G747"/>
+  <dimension ref="A1:G752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56531,6 +56716,191 @@
         </is>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:05+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>-37.3595913489825,175.93801446289132</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>-37.360298070403985,175.9378772420556</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-37.361008706281524,175.93776595657403</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-37.361722373249776,175.9376793695525</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>-37.36243807384352,175.9377086210067</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>-37.35959200438297,175.93802197775406</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>-37.360299227907866,175.93789138457316</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>-37.36100953012007,175.93777945699068</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-37.361722518260805,175.93768320156497</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>-37.36243835188766,175.93771786682757</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:58:57+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>-37.35959200438297,175.93802197775406</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>-37.360299227907866,175.93789138457316</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>-37.36100931729527,175.93777596938304</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-37.361722518260805,175.93768320156497</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>-37.36243835188766,175.93771786682757</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>-37.3595914174572,175.93801524802623</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>-37.36029888800612,175.93788723161163</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>-37.361008438533666,175.93776156893864</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-37.36172207896228,175.9376715928214</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>-37.36243798568304,175.93770568940496</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>-37.35958989144836,175.93799775073424</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>-37.3602978591134,175.937874660485</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-37.36100729888709,175.93774289336264</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-37.36172160980723,175.9376591951342</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-37.362437473672614,175.9376886635642</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
